--- a/Marine_Operations_Performance_Dataset.xlsx
+++ b/Marine_Operations_Performance_Dataset.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$159</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="359">
   <si>
     <t>DATE</t>
   </si>
@@ -1032,16 +1032,85 @@
     <t>Tank Slab Installation</t>
   </si>
   <si>
-    <t>5.Feb.2026</t>
-  </si>
-  <si>
     <t>Receipt of two patrol boats from police headquarters</t>
+  </si>
+  <si>
+    <t>Start DATE</t>
+  </si>
+  <si>
+    <t>Completion Date</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Photo Evidence</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Lutembe beach</t>
+  </si>
+  <si>
+    <t>Visiting scene of drowning</t>
+  </si>
+  <si>
+    <t>Operations; Diving</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Enforcement of safety rules and regulations Jan- March 2026</t>
+  </si>
+  <si>
+    <t>Hama</t>
+  </si>
+  <si>
+    <t>CPL Oula</t>
+  </si>
+  <si>
+    <t>Boat repair</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Rest TV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP Nahabwe </t>
+  </si>
+  <si>
+    <t>Initial marine training</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Capacity Building Jan- March 2026</t>
+  </si>
+  <si>
+    <t>AIP Ariko; AIP Komakech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handover and taking over  </t>
+  </si>
+  <si>
+    <t>Panyimur detach</t>
+  </si>
+  <si>
+    <t>Administration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1151,7 +1220,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1184,6 +1253,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3271,3693 +3347,4165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="83.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="83.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.75" thickBot="1">
+    <row r="1" spans="1:9" ht="30.75" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="46.5" hidden="1" customHeight="1" thickBot="1">
+      <c r="H1" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="46.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A2" s="3">
         <v>45751</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A3" s="3">
         <v>45756</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>5</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="4" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A4" s="3">
         <v>45758</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A5" s="3">
         <v>45771</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>20</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="6" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A6" s="3">
         <v>45772</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>30</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A7" s="3">
         <v>45756</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>30</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="1"/>
+      <c r="I7" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="8" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A8" s="3">
         <v>45797</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="9" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A9" s="3">
         <v>45813</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="10" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A10" s="3">
         <v>45818</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>80</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="1"/>
+      <c r="I10" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="11" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A11" s="3">
         <v>45821</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>30</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="34.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="12" spans="1:9" ht="34.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A12" s="3">
         <v>45828</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
         <v>19</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="13" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A13" s="3">
         <v>45828</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
         <v>8</v>
       </c>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A14" s="3">
         <v>45828</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A15" s="3">
         <v>45809</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1">
         <v>150</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="1"/>
+      <c r="I15" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="16" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A16" s="3">
         <v>45839</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1">
         <v>26</v>
       </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A17" s="3">
         <v>45840</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="18" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A18" s="3">
         <v>45840</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1">
         <v>20</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="1"/>
+      <c r="I18" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="19" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A19" s="3">
         <v>45841</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="14"/>
+      <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" hidden="1" thickBot="1">
       <c r="A20" s="3">
         <v>45842</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="14"/>
+      <c r="C20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A21" s="3">
         <v>45843</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="14"/>
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A22" s="3">
         <v>45847</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1">
         <v>100</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="1"/>
+      <c r="I22" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="23" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A23" s="3">
         <v>45863</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>50</v>
       </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A24" s="3">
         <v>45847</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>59</v>
       </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A25" s="3">
         <v>45877</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>6</v>
       </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A26" s="3">
         <v>45891</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="14"/>
+      <c r="C26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="27" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A27" s="3">
         <v>45870</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="14"/>
+      <c r="C27" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="28" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A28" s="3">
         <v>45894</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="14"/>
+      <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>100</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="1"/>
+      <c r="I28" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60.75" hidden="1" thickBot="1">
+    <row r="29" spans="1:9" ht="60.75" hidden="1" thickBot="1">
       <c r="A29" s="3">
         <v>45894</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>20</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="1"/>
+      <c r="I29" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" hidden="1" thickBot="1">
+    <row r="30" spans="1:9" ht="15.75" hidden="1" thickBot="1">
       <c r="A30" s="3">
         <v>45894</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="31" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A31" s="3">
         <v>45896</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="14"/>
+      <c r="C31" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1">
         <v>20</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="1"/>
+      <c r="I31" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="60.75" hidden="1" thickBot="1">
+    <row r="32" spans="1:9" ht="60.75" hidden="1" thickBot="1">
       <c r="A32" s="3">
         <v>45896</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>48</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="1"/>
+      <c r="I32" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="33" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A33" s="3">
         <v>45896</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="34" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A34" s="3">
         <v>45897</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>70</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="H34" s="1"/>
+      <c r="I34" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="35" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A35" s="3">
         <v>45897</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="14"/>
+      <c r="C35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F35" s="1">
+      <c r="G35" s="1">
         <v>44</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="H35" s="1"/>
+      <c r="I35" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="36" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A36" s="3">
         <v>45897</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="14"/>
+      <c r="C36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1">
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
         <v>6</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="1"/>
+      <c r="I36" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="37" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A37" s="3">
         <v>45899</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="14"/>
+      <c r="C37" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>50</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="1"/>
+      <c r="I37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="38" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A38" s="3">
         <v>45903</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1">
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
         <v>20</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="H38" s="1"/>
+      <c r="I38" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="60.75" hidden="1" thickBot="1">
+    <row r="39" spans="1:9" ht="60.75" hidden="1" thickBot="1">
       <c r="A39" s="3">
         <v>45898</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="14"/>
+      <c r="C39" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1">
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="H39" s="1"/>
+      <c r="I39" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="40" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A40" s="3">
         <v>45903</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="14"/>
+      <c r="C40" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1">
         <v>20</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="H40" s="1"/>
+      <c r="I40" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="41" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A41" s="3">
         <v>45904</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="14"/>
+      <c r="C41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1">
         <v>8</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="H41" s="1"/>
+      <c r="I41" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="42" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A42" s="3">
         <v>45904</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="14"/>
+      <c r="C42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1">
         <v>8</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="1"/>
+      <c r="I42" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="43" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A43" s="3">
         <v>45905</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="14"/>
+      <c r="C43" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1">
         <v>5</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="1"/>
+      <c r="I43" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="44" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A44" s="3">
         <v>45905</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="14"/>
+      <c r="C44" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1">
         <v>5</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="1"/>
+      <c r="I44" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="45" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A45" s="3">
         <v>45905</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="14"/>
+      <c r="C45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1">
         <v>25</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="1"/>
+      <c r="I45" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="46" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A46" s="3">
         <v>45905</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="14"/>
+      <c r="C46" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1">
         <v>6</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="1"/>
+      <c r="I46" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="47" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A47" s="3">
         <v>45906</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="14"/>
+      <c r="C47" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1">
         <v>30</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="1"/>
+      <c r="I47" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="48" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A48" s="3">
         <v>45910</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="14"/>
+      <c r="C48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>30</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="1"/>
+      <c r="I48" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="75.75" hidden="1" thickBot="1">
+    <row r="49" spans="1:9" ht="75.75" hidden="1" thickBot="1">
       <c r="A49" s="3">
         <v>45908</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="14"/>
+      <c r="C49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>10</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="H49" s="1"/>
+      <c r="I49" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="60.75" hidden="1" thickBot="1">
+    <row r="50" spans="1:9" ht="60.75" hidden="1" thickBot="1">
       <c r="A50" s="3">
         <v>45909</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="14"/>
+      <c r="C50" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1">
+      <c r="F50" s="1"/>
+      <c r="G50" s="1">
         <v>50</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="1"/>
+      <c r="I50" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="75.75" hidden="1" thickBot="1">
+    <row r="51" spans="1:9" ht="75.75" hidden="1" thickBot="1">
       <c r="A51" s="3">
         <v>45911</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="1">
+      <c r="G51" s="1">
         <v>150</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="1"/>
+      <c r="I51" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="52" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A52" s="3">
         <v>45911</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="14"/>
+      <c r="C52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <v>100</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="H52" s="1"/>
+      <c r="I52" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="53" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A53" s="3">
         <v>45913</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="14"/>
+      <c r="C53" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
         <v>50</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="H53" s="1"/>
+      <c r="I53" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="54" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A54" s="3">
         <v>45916</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="14"/>
+      <c r="C54" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="55" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A55" s="3">
         <v>45915</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="14"/>
+      <c r="C55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1">
         <v>30</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="H55" s="1"/>
+      <c r="I55" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="56" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A56" s="3">
         <v>45916</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="14"/>
+      <c r="C56" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1">
         <v>20</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="H56" s="1"/>
+      <c r="I56" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="57" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A57" s="3">
         <v>45917</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1" t="s">
+      <c r="B57" s="14"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="58" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A58" s="3">
         <v>45919</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="14"/>
+      <c r="C58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F58" s="1">
+      <c r="G58" s="1">
         <v>5</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="1"/>
+      <c r="I58" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" hidden="1" thickBot="1">
+    <row r="59" spans="1:9" ht="15.75" hidden="1" thickBot="1">
       <c r="A59" s="3">
         <v>45919</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="14"/>
+      <c r="C59" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="2" t="s">
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="60" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A60" s="3">
         <v>45916</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="14"/>
+      <c r="C60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="61" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A61" s="3">
         <v>45922</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="14"/>
+      <c r="C61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1">
         <v>100</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="1"/>
+      <c r="I61" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="62" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A62" s="3">
         <v>45923</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="14"/>
+      <c r="C62" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1">
         <v>100</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="1"/>
+      <c r="I62" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="63" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A63" s="3">
         <v>45924</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="14"/>
+      <c r="C63" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1">
         <v>100</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="1"/>
+      <c r="I63" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="64" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A64" s="3">
         <v>45924</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="14"/>
+      <c r="C64" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F64" s="1">
+      <c r="G64" s="1">
         <v>80</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="H64" s="1"/>
+      <c r="I64" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="60.75" hidden="1" thickBot="1">
+    <row r="65" spans="1:9" ht="60.75" hidden="1" thickBot="1">
       <c r="A65" s="3">
         <v>45925</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="14"/>
+      <c r="C65" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1">
         <v>90</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="H65" s="1"/>
+      <c r="I65" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="90.75" hidden="1" thickBot="1">
+    <row r="66" spans="1:9" ht="90.75" hidden="1" thickBot="1">
       <c r="A66" s="3">
         <v>45926</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1" t="s">
+      <c r="B66" s="14"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="H66" s="1"/>
+      <c r="I66" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="67" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A67" s="3">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="14"/>
+      <c r="C67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1">
+      <c r="F67" s="1"/>
+      <c r="G67" s="1">
         <v>120</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="H67" s="1"/>
+      <c r="I67" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="30.75" hidden="1" thickBot="1">
+    <row r="68" spans="1:9" ht="30.75" hidden="1" thickBot="1">
       <c r="A68" s="3">
         <v>45930</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="14"/>
+      <c r="C68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1">
+      <c r="F68" s="1"/>
+      <c r="G68" s="1">
         <v>100</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="H68" s="1"/>
+      <c r="I68" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="45.75" hidden="1" thickBot="1">
+    <row r="69" spans="1:9" ht="45.75" hidden="1" thickBot="1">
       <c r="A69" s="3"/>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="14"/>
+      <c r="C69" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="1"/>
+      <c r="E69" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="30.75" thickBot="1">
+    <row r="70" spans="1:9" ht="30.75" thickBot="1">
       <c r="A70" s="3">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="14"/>
+      <c r="C70" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="45.75" thickBot="1">
+    <row r="71" spans="1:9" ht="45.75" thickBot="1">
       <c r="A71" s="3">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="14"/>
+      <c r="C71" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="1"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="30.75" thickBot="1">
+    <row r="72" spans="1:9" ht="30.75" thickBot="1">
       <c r="A72" s="3">
         <v>45931</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="14"/>
+      <c r="C72" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="1">
+      <c r="G72" s="1">
         <v>6</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="15"/>
+      <c r="I72" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30.75" thickBot="1">
+    <row r="73" spans="1:9" ht="30.75" thickBot="1">
       <c r="A73" s="3">
         <v>45931</v>
       </c>
-      <c r="B73" s="1"/>
+      <c r="B73" s="14"/>
       <c r="C73" s="1"/>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1">
+      <c r="F73" s="1"/>
+      <c r="G73" s="1">
         <v>30</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="H73" s="15"/>
+      <c r="I73" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="45.75" thickBot="1">
+    <row r="74" spans="1:9" ht="45.75" thickBot="1">
       <c r="A74" s="3">
         <v>45932</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="14"/>
+      <c r="C74" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1">
+      <c r="F74" s="1"/>
+      <c r="G74" s="1">
         <v>100</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="15"/>
+      <c r="I74" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="30.75" thickBot="1">
+    <row r="75" spans="1:9" ht="30.75" thickBot="1">
       <c r="A75" s="3">
         <v>45932</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="14"/>
+      <c r="C75" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1">
+      <c r="F75" s="1"/>
+      <c r="G75" s="1">
         <v>150</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="H75" s="15"/>
+      <c r="I75" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="30.75" thickBot="1">
+    <row r="76" spans="1:9" ht="30.75" thickBot="1">
       <c r="A76" s="3">
         <v>45932</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="14"/>
+      <c r="C76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1">
+      <c r="F76" s="1"/>
+      <c r="G76" s="1">
         <v>100</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="15"/>
+      <c r="I76" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="30.75" thickBot="1">
+    <row r="77" spans="1:9" ht="30.75" thickBot="1">
       <c r="A77" s="3">
         <v>45932</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="14"/>
+      <c r="C77" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="1"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="30.75" thickBot="1">
+    <row r="78" spans="1:9" ht="30.75" thickBot="1">
       <c r="A78" s="3">
         <v>45932</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="14"/>
+      <c r="C78" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1">
+      <c r="F78" s="1"/>
+      <c r="G78" s="1">
         <v>10</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="15"/>
+      <c r="I78" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="30.75" thickBot="1">
+    <row r="79" spans="1:9" ht="30.75" thickBot="1">
       <c r="A79" s="3">
         <v>45933</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="14"/>
+      <c r="C79" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1">
+      <c r="F79" s="1"/>
+      <c r="G79" s="1">
         <v>70</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="H79" s="15"/>
+      <c r="I79" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="45.75" thickBot="1">
+    <row r="80" spans="1:9" ht="45.75" thickBot="1">
       <c r="A80" s="3">
         <v>45937</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="14"/>
+      <c r="C80" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1">
+      <c r="F80" s="1"/>
+      <c r="G80" s="1">
         <v>100</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="H80" s="15"/>
+      <c r="I80" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="30.75" thickBot="1">
+    <row r="81" spans="1:9" ht="30.75" thickBot="1">
       <c r="A81" s="3">
         <v>45938</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="14"/>
+      <c r="C81" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1">
+      <c r="F81" s="1"/>
+      <c r="G81" s="1">
         <v>100</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="H81" s="15"/>
+      <c r="I81" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="30.75" thickBot="1">
+    <row r="82" spans="1:9" ht="30.75" thickBot="1">
       <c r="A82" s="3">
         <v>45938</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="14"/>
+      <c r="C82" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1">
+      <c r="F82" s="1"/>
+      <c r="G82" s="1">
         <v>100</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="H82" s="15"/>
+      <c r="I82" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="45.75" thickBot="1">
+    <row r="83" spans="1:9" ht="45.75" thickBot="1">
       <c r="A83" s="3">
         <v>45931</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="14"/>
+      <c r="C83" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1">
+      <c r="F83" s="1"/>
+      <c r="G83" s="1">
         <v>8</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="H83" s="15"/>
+      <c r="I83" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="30.75" thickBot="1">
+    <row r="84" spans="1:9" ht="30.75" thickBot="1">
       <c r="A84" s="3">
         <v>45933</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="14"/>
+      <c r="C84" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1">
+      <c r="F84" s="1"/>
+      <c r="G84" s="1">
         <v>100</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="H84" s="15"/>
+      <c r="I84" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="60.75" thickBot="1">
+    <row r="85" spans="1:9" ht="60.75" thickBot="1">
       <c r="A85" s="3">
         <v>45933</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="14"/>
+      <c r="C85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="1"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="60.75" thickBot="1">
+    <row r="86" spans="1:9" ht="60.75" thickBot="1">
       <c r="A86" s="3">
         <v>45941</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="14"/>
+      <c r="C86" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="1">
+      <c r="G86" s="1">
         <v>6</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="H86" s="15"/>
+      <c r="I86" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="30.75" thickBot="1">
+    <row r="87" spans="1:9" ht="30.75" thickBot="1">
       <c r="A87" s="3">
         <v>45941</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="14"/>
+      <c r="C87" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F87" s="1">
+      <c r="G87" s="1">
         <v>51</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="H87" s="15"/>
+      <c r="I87" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="30.75" thickBot="1">
+    <row r="88" spans="1:9" ht="30.75" thickBot="1">
       <c r="A88" s="3">
         <v>45943</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="14"/>
+      <c r="C88" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1">
+      <c r="F88" s="1"/>
+      <c r="G88" s="1">
         <v>50</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="H88" s="15"/>
+      <c r="I88" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="45.75" thickBot="1">
+    <row r="89" spans="1:9" ht="45.75" thickBot="1">
       <c r="A89" s="3">
         <v>45946</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="14"/>
+      <c r="C89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1">
+      <c r="F89" s="1"/>
+      <c r="G89" s="1">
         <v>10</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="H89" s="15"/>
+      <c r="I89" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="60.75" thickBot="1">
+    <row r="90" spans="1:9" ht="60.75" thickBot="1">
       <c r="A90" s="3">
         <v>45946</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="14"/>
+      <c r="C90" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1">
+      <c r="F90" s="1"/>
+      <c r="G90" s="1">
         <v>10</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="H90" s="15"/>
+      <c r="I90" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="30.75" thickBot="1">
+    <row r="91" spans="1:9" ht="30.75" thickBot="1">
       <c r="A91" s="3">
         <v>45949</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="14"/>
+      <c r="C91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F91" s="1"/>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="1"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="30.75" thickBot="1">
+    <row r="92" spans="1:9" ht="30.75" thickBot="1">
       <c r="A92" s="3">
         <v>45950</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="14"/>
+      <c r="C92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="E92" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1">
+      <c r="F92" s="1"/>
+      <c r="G92" s="1">
         <v>100</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="H92" s="15"/>
+      <c r="I92" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="45.75" thickBot="1">
+    <row r="93" spans="1:9" ht="45.75" thickBot="1">
       <c r="A93" s="3">
         <v>45950</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="14"/>
+      <c r="C93" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="1"/>
+      <c r="F93" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F93" s="1">
+      <c r="G93" s="1">
         <v>50</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="H93" s="15"/>
+      <c r="I93" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="45.75" thickBot="1">
+    <row r="94" spans="1:9" ht="45.75" thickBot="1">
       <c r="A94" s="3">
         <v>45951</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="14"/>
+      <c r="C94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1">
+      <c r="F94" s="1"/>
+      <c r="G94" s="1">
         <v>200</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="H94" s="15"/>
+      <c r="I94" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="75.75" thickBot="1">
+    <row r="95" spans="1:9" ht="75.75" thickBot="1">
       <c r="A95" s="3">
         <v>45952</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="14"/>
+      <c r="C95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1">
+      <c r="F95" s="1"/>
+      <c r="G95" s="1">
         <v>40</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="H95" s="15"/>
+      <c r="I95" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="75.75" thickBot="1">
+    <row r="96" spans="1:9" ht="75.75" thickBot="1">
       <c r="A96" s="3">
         <v>45956</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="14"/>
+      <c r="C96" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1">
+      <c r="F96" s="1"/>
+      <c r="G96" s="1">
         <v>10</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="H96" s="15"/>
+      <c r="I96" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="75.75" thickBot="1">
+    <row r="97" spans="1:9" ht="75.75" thickBot="1">
       <c r="A97" s="3">
         <v>45957</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="14"/>
+      <c r="C97" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="E97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F97" s="1">
+      <c r="G97" s="1">
         <v>5</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="H97" s="15"/>
+      <c r="I97" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="30.75" thickBot="1">
+    <row r="98" spans="1:9" ht="30.75" thickBot="1">
       <c r="A98" s="3">
         <v>45958</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="14"/>
+      <c r="C98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1">
+      <c r="F98" s="1"/>
+      <c r="G98" s="1">
         <v>50</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="H98" s="15"/>
+      <c r="I98" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="75.75" thickBot="1">
+    <row r="99" spans="1:9" ht="75.75" thickBot="1">
       <c r="A99" s="3">
         <v>45945</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="14"/>
+      <c r="C99" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F99" s="1">
+      <c r="G99" s="1">
         <v>10</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="H99" s="15"/>
+      <c r="I99" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="30.75" thickBot="1">
+    <row r="100" spans="1:9" ht="30.75" thickBot="1">
       <c r="A100" s="3">
         <v>45953</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="14"/>
+      <c r="C100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="1"/>
+      <c r="H100" s="15"/>
+      <c r="I100" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="30.75" thickBot="1">
+    <row r="101" spans="1:9" ht="30.75" thickBot="1">
       <c r="A101" s="3">
         <v>45959</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="14"/>
+      <c r="C101" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1">
+      <c r="F101" s="1"/>
+      <c r="G101" s="1">
         <v>100</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="H101" s="15"/>
+      <c r="I101" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="30.75" thickBot="1">
+    <row r="102" spans="1:9" ht="30.75" thickBot="1">
       <c r="A102" s="3">
         <v>45960</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="14"/>
+      <c r="C102" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1">
+      <c r="F102" s="1"/>
+      <c r="G102" s="1">
         <v>100</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="H102" s="15"/>
+      <c r="I102" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="30.75" thickBot="1">
+    <row r="103" spans="1:9" ht="30.75" thickBot="1">
       <c r="A103" s="3">
         <v>45965</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="14"/>
+      <c r="C103" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="1"/>
+      <c r="H103" s="15"/>
+      <c r="I103" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="30.75" thickBot="1">
+    <row r="104" spans="1:9" ht="30.75" thickBot="1">
       <c r="A104" s="3">
         <v>45965</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="14"/>
+      <c r="C104" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="1"/>
       <c r="F104" s="1"/>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="1"/>
+      <c r="H104" s="15"/>
+      <c r="I104" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="45.75" thickBot="1">
+    <row r="105" spans="1:9" ht="45.75" thickBot="1">
       <c r="A105" s="3">
         <v>45965</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="14"/>
+      <c r="C105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="1"/>
+      <c r="H105" s="15"/>
+      <c r="I105" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="30.75" thickBot="1">
+    <row r="106" spans="1:9" ht="30.75" thickBot="1">
       <c r="A106" s="3">
         <v>45965</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="14"/>
+      <c r="C106" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="4" t="s">
+      <c r="G106" s="1"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="45.75" thickBot="1">
+    <row r="107" spans="1:9" ht="45.75" thickBot="1">
       <c r="A107" s="3">
         <v>45968</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="14"/>
+      <c r="C107" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="4" t="s">
+      <c r="G107" s="1"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="30.75" thickBot="1">
+    <row r="108" spans="1:9" ht="30.75" thickBot="1">
       <c r="A108" s="3">
         <v>45968</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="14"/>
+      <c r="C108" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1">
+      <c r="F108" s="1"/>
+      <c r="G108" s="1">
         <v>15</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="H108" s="15"/>
+      <c r="I108" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="30.75" thickBot="1">
+    <row r="109" spans="1:9" ht="30.75" thickBot="1">
       <c r="A109" s="3">
         <v>45969</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="14"/>
+      <c r="C109" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1">
+      <c r="F109" s="1"/>
+      <c r="G109" s="1">
         <v>34</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="H109" s="15"/>
+      <c r="I109" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="30.75" thickBot="1">
+    <row r="110" spans="1:9" ht="30.75" thickBot="1">
       <c r="A110" s="3">
         <v>45970</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="14"/>
+      <c r="C110" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E110" s="1"/>
       <c r="F110" s="1"/>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="1"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="30.75" thickBot="1">
+    <row r="111" spans="1:9" ht="30.75" thickBot="1">
       <c r="A111" s="3">
         <v>45971</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="14"/>
+      <c r="C111" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1">
+      <c r="F111" s="1"/>
+      <c r="G111" s="1">
         <v>5</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="H111" s="15"/>
+      <c r="I111" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="30.75" thickBot="1">
+    <row r="112" spans="1:9" ht="30.75" thickBot="1">
       <c r="A112" s="3">
         <v>45971</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="14"/>
+      <c r="C112" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1">
+      <c r="F112" s="1"/>
+      <c r="G112" s="1">
         <v>25</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="H112" s="15"/>
+      <c r="I112" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="30.75" thickBot="1">
+    <row r="113" spans="1:9" ht="30.75" thickBot="1">
       <c r="A113" s="3">
         <v>45972</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="14"/>
+      <c r="C113" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="1"/>
+      <c r="E113" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1">
+      <c r="F113" s="1"/>
+      <c r="G113" s="1">
         <v>100</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="H113" s="15"/>
+      <c r="I113" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="30.75" thickBot="1">
+    <row r="114" spans="1:9" ht="30.75" thickBot="1">
       <c r="A114" s="3">
         <v>45973</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="14"/>
+      <c r="C114" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="1"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="30.75" thickBot="1">
+    <row r="115" spans="1:9" ht="30.75" thickBot="1">
       <c r="A115" s="3">
         <v>45974</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="14"/>
+      <c r="C115" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="1"/>
+      <c r="H115" s="15"/>
+      <c r="I115" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="30.75" thickBot="1">
+    <row r="116" spans="1:9" ht="30.75" thickBot="1">
       <c r="A116" s="3">
         <v>45975</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="14"/>
+      <c r="C116" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1">
+      <c r="F116" s="1"/>
+      <c r="G116" s="1">
         <v>15</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="H116" s="15"/>
+      <c r="I116" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="45.75" thickBot="1">
+    <row r="117" spans="1:9" ht="45.75" thickBot="1">
       <c r="A117" s="3">
         <v>45976</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="14"/>
+      <c r="C117" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1">
+      <c r="F117" s="1"/>
+      <c r="G117" s="1">
         <v>4</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="H117" s="15"/>
+      <c r="I117" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="45.75" thickBot="1">
+    <row r="118" spans="1:9" ht="45.75" thickBot="1">
       <c r="A118" s="3">
         <v>45976</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="14"/>
+      <c r="C118" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1">
+      <c r="F118" s="1"/>
+      <c r="G118" s="1">
         <v>4</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="H118" s="15"/>
+      <c r="I118" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="30.75" thickBot="1">
+    <row r="119" spans="1:9" ht="30.75" thickBot="1">
       <c r="A119" s="3">
         <v>45976</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="14"/>
+      <c r="C119" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="4" t="s">
+      <c r="G119" s="1"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75" thickBot="1">
+    <row r="120" spans="1:9" ht="15.75" thickBot="1">
       <c r="A120" s="3">
         <v>45978</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="14"/>
+      <c r="C120" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E120" s="1"/>
       <c r="F120" s="1"/>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="1"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.75" thickBot="1">
+    <row r="121" spans="1:9" ht="15.75" thickBot="1">
       <c r="A121" s="3">
         <v>45978</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="14"/>
+      <c r="C121" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="1"/>
+      <c r="E121" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E121" s="1"/>
       <c r="F121" s="1"/>
-      <c r="G121" s="4" t="s">
+      <c r="G121" s="1"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="45.75" thickBot="1">
+    <row r="122" spans="1:9" ht="45.75" thickBot="1">
       <c r="A122" s="3">
         <v>45980</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="14"/>
+      <c r="C122" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1">
+      <c r="F122" s="1"/>
+      <c r="G122" s="1">
         <v>3</v>
       </c>
-      <c r="G122" s="4" t="s">
+      <c r="H122" s="15"/>
+      <c r="I122" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="45.75" thickBot="1">
+    <row r="123" spans="1:9" ht="45.75" thickBot="1">
       <c r="A123" s="3">
         <v>45980</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="14"/>
+      <c r="C123" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E123" s="1"/>
       <c r="F123" s="1"/>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="1"/>
+      <c r="H123" s="15"/>
+      <c r="I123" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="60.75" thickBot="1">
+    <row r="124" spans="1:9" ht="60.75" thickBot="1">
       <c r="A124" s="3">
         <v>45980</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="14"/>
+      <c r="C124" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1">
+      <c r="F124" s="1"/>
+      <c r="G124" s="1">
         <v>4</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="H124" s="15"/>
+      <c r="I124" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="45.75" thickBot="1">
+    <row r="125" spans="1:9" ht="45.75" thickBot="1">
       <c r="A125" s="3">
         <v>45980</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="14"/>
+      <c r="C125" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1">
+      <c r="F125" s="1"/>
+      <c r="G125" s="1">
         <v>30</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="H125" s="15"/>
+      <c r="I125" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="30.75" thickBot="1">
+    <row r="126" spans="1:9" ht="30.75" thickBot="1">
       <c r="A126" s="3">
         <v>45982</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="14"/>
+      <c r="C126" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="E126" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1">
+      <c r="F126" s="1"/>
+      <c r="G126" s="1">
         <v>30</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="H126" s="15"/>
+      <c r="I126" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="45.75" thickBot="1">
+    <row r="127" spans="1:9" ht="45.75" thickBot="1">
       <c r="A127" s="3">
         <v>45982</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="14"/>
+      <c r="C127" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1">
+      <c r="F127" s="1"/>
+      <c r="G127" s="1">
         <v>20</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="H127" s="15"/>
+      <c r="I127" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="30.75" thickBot="1">
+    <row r="128" spans="1:9" ht="30.75" thickBot="1">
       <c r="A128" s="3">
         <v>45986</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="14"/>
+      <c r="C128" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E128" s="1"/>
-      <c r="F128" s="1">
+      <c r="F128" s="1"/>
+      <c r="G128" s="1">
         <v>20</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="H128" s="15"/>
+      <c r="I128" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="60.75" thickBot="1">
+    <row r="129" spans="1:9" ht="60.75" thickBot="1">
       <c r="A129" s="3">
         <v>45978</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="14"/>
+      <c r="C129" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="E129" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E129" s="1"/>
       <c r="F129" s="1"/>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="1"/>
+      <c r="H129" s="15"/>
+      <c r="I129" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="45.75" thickBot="1">
+    <row r="130" spans="1:9" ht="45.75" thickBot="1">
       <c r="A130" s="3">
         <v>45982</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="14"/>
+      <c r="C130" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="E130" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1">
+      <c r="F130" s="1"/>
+      <c r="G130" s="1">
         <v>10</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="H130" s="15"/>
+      <c r="I130" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="30.75" thickBot="1">
+    <row r="131" spans="1:9" ht="30.75" thickBot="1">
       <c r="A131" s="3">
         <v>45988</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="14"/>
+      <c r="C131" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="E131" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1">
+      <c r="F131" s="1"/>
+      <c r="G131" s="1">
         <v>10</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="H131" s="15"/>
+      <c r="I131" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="60.75" thickBot="1">
+    <row r="132" spans="1:9" ht="60.75" thickBot="1">
       <c r="A132" s="3">
         <v>45989</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="14"/>
+      <c r="C132" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1">
+      <c r="F132" s="1"/>
+      <c r="G132" s="1">
         <v>100</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="H132" s="15"/>
+      <c r="I132" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="45.75" thickBot="1">
+    <row r="133" spans="1:9" ht="45.75" thickBot="1">
       <c r="A133" s="3">
         <v>45989</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="14"/>
+      <c r="C133" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1">
+      <c r="F133" s="1"/>
+      <c r="G133" s="1">
         <v>20</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="H133" s="15"/>
+      <c r="I133" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="30.75" thickBot="1">
+    <row r="134" spans="1:9" ht="30.75" thickBot="1">
       <c r="A134" s="3">
         <v>45992</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="14"/>
+      <c r="C134" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="1"/>
+      <c r="E134" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1">
+      <c r="F134" s="1"/>
+      <c r="G134" s="1">
         <v>15</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="H134" s="15"/>
+      <c r="I134" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="45.75" thickBot="1">
+    <row r="135" spans="1:9" ht="45.75" thickBot="1">
       <c r="A135" s="3">
         <v>45982</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B135" s="14"/>
+      <c r="C135" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1">
+      <c r="F135" s="1"/>
+      <c r="G135" s="1">
         <v>50</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="H135" s="15"/>
+      <c r="I135" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.75" thickBot="1">
+    <row r="136" spans="1:9" ht="15.75" thickBot="1">
       <c r="A136" s="3">
         <v>45993</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="14"/>
+      <c r="C136" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="1"/>
+      <c r="E136" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="1"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="30.75" thickBot="1">
+    <row r="137" spans="1:9" ht="30.75" thickBot="1">
       <c r="A137" s="3">
         <v>45993</v>
       </c>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1" t="s">
+      <c r="B137" s="14"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="4" t="s">
+      <c r="G137" s="1"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="30.75" thickBot="1">
+    <row r="138" spans="1:9" ht="30.75" thickBot="1">
       <c r="A138" s="3">
         <v>45994</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B138" s="14"/>
+      <c r="C138" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="1"/>
+      <c r="H138" s="15"/>
+      <c r="I138" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="45.75" thickBot="1">
+    <row r="139" spans="1:9" ht="45.75" thickBot="1">
       <c r="A139" s="3">
         <v>45996</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="14"/>
+      <c r="C139" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1">
+      <c r="F139" s="1"/>
+      <c r="G139" s="1">
         <v>103</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="H139" s="15"/>
+      <c r="I139" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="30.75" thickBot="1">
+    <row r="140" spans="1:9" ht="30.75" thickBot="1">
       <c r="A140" s="3">
         <v>45999</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="14"/>
+      <c r="C140" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1">
+      <c r="F140" s="1"/>
+      <c r="G140" s="1">
         <v>20</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="H140" s="15"/>
+      <c r="I140" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.75" thickBot="1">
+    <row r="141" spans="1:9" ht="15.75" thickBot="1">
       <c r="A141" s="3">
         <v>46000</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="14"/>
+      <c r="C141" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1">
+      <c r="F141" s="1"/>
+      <c r="G141" s="1">
         <v>20</v>
       </c>
-      <c r="G141" s="4" t="s">
+      <c r="H141" s="15"/>
+      <c r="I141" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="60.75" thickBot="1">
+    <row r="142" spans="1:9" ht="60.75" thickBot="1">
       <c r="A142" s="3">
         <v>45999</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="14"/>
+      <c r="C142" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="F142" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F142" s="1">
+      <c r="G142" s="1">
         <v>62</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="H142" s="15"/>
+      <c r="I142" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="60.75" thickBot="1">
+    <row r="143" spans="1:9" ht="60.75" thickBot="1">
       <c r="A143" s="3">
         <v>46004</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="14"/>
+      <c r="C143" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E143" s="1"/>
-      <c r="F143" s="1">
+      <c r="F143" s="1"/>
+      <c r="G143" s="1">
         <v>12</v>
       </c>
-      <c r="G143" s="4" t="s">
+      <c r="H143" s="15"/>
+      <c r="I143" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.75" thickBot="1">
+    <row r="144" spans="1:9" ht="15.75" thickBot="1">
       <c r="A144" s="3">
         <v>46005</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="14"/>
+      <c r="C144" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="4" t="s">
+      <c r="G144" s="1"/>
+      <c r="H144" s="15"/>
+      <c r="I144" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="45.75" thickBot="1">
+    <row r="145" spans="1:9" ht="45.75" thickBot="1">
       <c r="A145" s="3">
         <v>45992</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="14"/>
+      <c r="C145" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E145" s="1"/>
-      <c r="F145" s="1">
+      <c r="F145" s="1"/>
+      <c r="G145" s="1">
         <v>5</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="H145" s="15"/>
+      <c r="I145" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="30.75" thickBot="1">
+    <row r="146" spans="1:9" ht="30.75" thickBot="1">
       <c r="A146" s="3">
         <v>45982</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="14"/>
+      <c r="C146" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E146" s="1"/>
-      <c r="F146" s="1">
+      <c r="F146" s="1"/>
+      <c r="G146" s="1">
         <v>3</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="H146" s="15"/>
+      <c r="I146" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="45.75" thickBot="1">
+    <row r="147" spans="1:9" ht="45.75" thickBot="1">
       <c r="A147" s="3">
         <v>45986</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="14"/>
+      <c r="C147" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E147" s="1"/>
-      <c r="F147" s="1">
+      <c r="F147" s="1"/>
+      <c r="G147" s="1">
         <v>3</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="H147" s="15"/>
+      <c r="I147" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="30.75" thickBot="1">
+    <row r="148" spans="1:9" ht="30.75" thickBot="1">
       <c r="A148" s="3">
         <v>45982</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B148" s="14"/>
+      <c r="C148" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="4" t="s">
+      <c r="G148" s="1"/>
+      <c r="H148" s="15"/>
+      <c r="I148" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="30.75" thickBot="1">
+    <row r="149" spans="1:9" ht="30.75" thickBot="1">
       <c r="A149" s="3">
         <v>45992</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B149" s="14"/>
+      <c r="C149" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="E149" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E149" s="1"/>
       <c r="F149" s="1"/>
-      <c r="G149" s="4" t="s">
+      <c r="G149" s="1"/>
+      <c r="H149" s="15"/>
+      <c r="I149" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="30.75" thickBot="1">
+    <row r="150" spans="1:9" ht="30.75" thickBot="1">
       <c r="A150" s="3">
         <v>45985</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="14"/>
+      <c r="C150" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="E150" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="1"/>
+      <c r="H150" s="15"/>
+      <c r="I150" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30.75" thickBot="1">
+    <row r="151" spans="1:9" ht="30.75" thickBot="1">
       <c r="A151" s="3">
         <v>46002</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="14"/>
+      <c r="C151" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="1"/>
+      <c r="H151" s="15"/>
+      <c r="I151" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="30.75" thickBot="1">
+    <row r="152" spans="1:9" ht="30.75" thickBot="1">
       <c r="A152" s="3">
         <v>45973</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B152" s="14"/>
+      <c r="C152" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E152" s="1"/>
       <c r="F152" s="1"/>
-      <c r="G152" s="4" t="s">
+      <c r="G152" s="1"/>
+      <c r="H152" s="15"/>
+      <c r="I152" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="30.75" thickBot="1">
+    <row r="153" spans="1:9" ht="30.75" thickBot="1">
       <c r="A153" s="3">
         <v>45964</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B153" s="14"/>
+      <c r="C153" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="E153" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E153" s="1"/>
       <c r="F153" s="1"/>
-      <c r="G153" s="4" t="s">
+      <c r="G153" s="1"/>
+      <c r="H153" s="15"/>
+      <c r="I153" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="30.75" thickBot="1">
+    <row r="154" spans="1:9" ht="30.75" thickBot="1">
       <c r="A154" s="3">
         <v>46001</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="14"/>
+      <c r="C154" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="E154" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="1"/>
       <c r="F154" s="1"/>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="1"/>
+      <c r="H154" s="15"/>
+      <c r="I154" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="30.75" thickBot="1">
+    <row r="155" spans="1:9" ht="30.75" thickBot="1">
       <c r="A155" s="3">
         <v>45958</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="14"/>
+      <c r="C155" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="E155" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E155" s="1"/>
       <c r="F155" s="1"/>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="1"/>
+      <c r="H155" s="15"/>
+      <c r="I155" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="30.75" thickBot="1">
+    <row r="156" spans="1:9" ht="30.75" thickBot="1">
       <c r="A156" s="3">
         <v>45973</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B156" s="14"/>
+      <c r="C156" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="E156" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E156" s="1"/>
       <c r="F156" s="1"/>
-      <c r="G156" s="4" t="s">
+      <c r="G156" s="1"/>
+      <c r="H156" s="15"/>
+      <c r="I156" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="30.75" thickBot="1">
+    <row r="157" spans="1:9" ht="30.75" thickBot="1">
       <c r="A157" s="3">
         <v>45973</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" s="14"/>
+      <c r="C157" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="E157" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="1"/>
+      <c r="H157" s="15"/>
+      <c r="I157" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="30.75" thickBot="1">
+    <row r="158" spans="1:9" ht="30.75" thickBot="1">
       <c r="A158" s="3">
         <v>46007</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B158" s="14"/>
+      <c r="C158" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="4" t="s">
+      <c r="G158" s="1"/>
+      <c r="H158" s="15"/>
+      <c r="I158" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="61.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="159" spans="1:9" ht="61.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A159" s="3">
         <v>45890</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B159" s="14"/>
+      <c r="C159" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1" t="s">
+      <c r="D159" s="1"/>
+      <c r="E159" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="F159" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F159" s="1"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7" ht="45">
+      <c r="G159" s="1"/>
+      <c r="H159" s="1"/>
+      <c r="I159" s="2"/>
+    </row>
+    <row r="160" spans="1:9" ht="45">
       <c r="A160" s="10">
         <v>46023</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="10"/>
+      <c r="C160" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="C160" s="11" t="s">
+      <c r="D160" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>294</v>
       </c>
-      <c r="E160" s="12" t="s">
+      <c r="F160" s="12" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="45">
+    <row r="161" spans="1:9" ht="45">
       <c r="A161" s="10">
         <v>46023</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="10"/>
+      <c r="C161" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
         <v>294</v>
       </c>
-      <c r="E161" s="12" t="s">
+      <c r="F161" s="12" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="60">
+    <row r="162" spans="1:9" ht="60">
       <c r="A162" s="10">
         <v>46031</v>
       </c>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="10"/>
+      <c r="C162" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C162" s="13" t="s">
+      <c r="D162" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D162" s="13" t="s">
+      <c r="E162" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="E162" s="13" t="s">
+      <c r="F162" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="F162">
+      <c r="G162">
         <v>20</v>
       </c>
-      <c r="G162" s="4" t="s">
+      <c r="I162" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="30">
+    <row r="163" spans="1:9" ht="30">
       <c r="A163" s="10">
         <v>46034</v>
       </c>
-      <c r="C163" s="13" t="s">
+      <c r="B163" s="10"/>
+      <c r="D163" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>302</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="I163" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:9">
       <c r="A164" s="10">
         <v>46055</v>
       </c>
-      <c r="B164" s="13" t="s">
+      <c r="B164" s="10"/>
+      <c r="C164" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C164" s="13" t="s">
+      <c r="D164" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>44</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="I164" s="4" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:9">
       <c r="A165" s="10">
         <v>46056</v>
       </c>
-      <c r="B165" s="13" t="s">
+      <c r="B165" s="10"/>
+      <c r="C165" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C165" s="13" t="s">
+      <c r="D165" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>90</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>303</v>
       </c>
-      <c r="F165">
+      <c r="G165">
         <v>20</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="I165" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:9">
       <c r="A166" s="10">
         <v>46028</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" s="10"/>
+      <c r="C166" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C166" s="13" t="s">
+      <c r="D166" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>305</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>306</v>
       </c>
-      <c r="G166" s="4" t="s">
+      <c r="I166" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:9">
       <c r="A167" s="10">
         <v>46032</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" s="10"/>
+      <c r="C167" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="C167" s="13" t="s">
+      <c r="D167" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>100</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="I167" s="4" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:9">
       <c r="A168" s="10">
         <v>46034</v>
       </c>
-      <c r="B168" s="13" t="s">
+      <c r="B168" s="10"/>
+      <c r="C168" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>309</v>
       </c>
-      <c r="G168" s="4" t="s">
+      <c r="I168" s="4" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="30">
+    <row r="169" spans="1:9" ht="30">
       <c r="A169" s="10">
         <v>46034</v>
       </c>
-      <c r="B169" s="13" t="s">
+      <c r="B169" s="10"/>
+      <c r="C169" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="C169" s="13" t="s">
+      <c r="D169" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
         <v>311</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>312</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="I169" s="4" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:9">
       <c r="A170" s="10">
         <v>46034</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" s="10"/>
+      <c r="C170" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="C170" s="13" t="s">
+      <c r="D170" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
         <v>315</v>
       </c>
-      <c r="G170" s="4" t="s">
+      <c r="I170" s="4" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="30">
+    <row r="171" spans="1:9" ht="30">
       <c r="A171" s="10">
         <v>46044</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" s="10"/>
+      <c r="C171" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="C171" s="13" t="s">
+      <c r="D171" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>317</v>
       </c>
-      <c r="F171">
+      <c r="G171">
         <v>10</v>
       </c>
-      <c r="G171" s="4" t="s">
+      <c r="I171" s="4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="30">
+    <row r="172" spans="1:9" ht="30">
       <c r="A172" s="10">
         <v>46044</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" s="10"/>
+      <c r="C172" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="C172" s="13" t="s">
+      <c r="D172" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>319</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="I172" s="4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:9">
       <c r="A173" s="10">
         <v>46044</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" s="10"/>
+      <c r="C173" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C173" s="13" t="s">
+      <c r="D173" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>44</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="I173" s="4" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="30">
+    <row r="174" spans="1:9" ht="30">
       <c r="A174" s="10">
         <v>46048</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" s="10"/>
+      <c r="C174" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C174" s="13" t="s">
+      <c r="D174" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>320</v>
       </c>
-      <c r="G174" s="4" t="s">
+      <c r="I174" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="30">
+    <row r="175" spans="1:9" ht="30">
       <c r="A175" s="10">
         <v>46048</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" s="10"/>
+      <c r="C175" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C175" s="13" t="s">
+      <c r="D175" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>321</v>
       </c>
-      <c r="G175" s="4" t="s">
+      <c r="I175" s="4" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30">
+    <row r="176" spans="1:9" ht="30">
       <c r="A176" s="10">
         <v>46049</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="10"/>
+      <c r="C176" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C176" s="13" t="s">
+      <c r="D176" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>322</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="I176" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:9">
       <c r="A177" s="10">
         <v>46049</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" s="10"/>
+      <c r="C177" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>323</v>
       </c>
-      <c r="G177" s="4" t="s">
+      <c r="I177" s="4" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:9">
       <c r="A178" s="10">
         <v>46051</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" s="10"/>
+      <c r="C178" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C178" s="13" t="s">
+      <c r="D178" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>324</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="I178" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="30">
+    <row r="179" spans="1:9" ht="30">
       <c r="A179" s="10">
         <v>46053</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" s="10"/>
+      <c r="C179" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C179" s="13" t="s">
+      <c r="D179" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>44</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="I179" s="4" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="30">
+    <row r="180" spans="1:9" ht="30">
       <c r="A180" s="10">
         <v>46058</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" s="10"/>
+      <c r="C180" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C180" s="13" t="s">
+      <c r="D180" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>332</v>
       </c>
-      <c r="F180">
+      <c r="G180">
         <v>11</v>
       </c>
-      <c r="G180" s="4" t="s">
+      <c r="I180" s="4" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:9">
       <c r="A181" s="10">
         <v>46058</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" s="10"/>
+      <c r="C181" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C181" s="13" t="s">
+      <c r="D181" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>333</v>
       </c>
-      <c r="G181" s="4" t="s">
+      <c r="I181" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
-      <c r="A182" t="s">
-        <v>335</v>
-      </c>
-      <c r="B182" s="13" t="s">
+    <row r="182" spans="1:9">
+      <c r="A182" s="16">
+        <v>46058</v>
+      </c>
+      <c r="C182" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C182" s="13" t="s">
+      <c r="D182" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>334</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="I182" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="30">
+    <row r="183" spans="1:9" ht="30">
       <c r="A183" s="10">
         <v>46059</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" s="10"/>
+      <c r="C183" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C183" s="13" t="s">
+      <c r="D183" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D183" t="s">
-        <v>336</v>
-      </c>
-      <c r="F183">
+      <c r="E183" t="s">
+        <v>335</v>
+      </c>
+      <c r="G183">
         <v>5</v>
       </c>
-      <c r="G183" s="4" t="s">
+      <c r="I183" s="4" t="s">
         <v>325</v>
       </c>
     </row>
+    <row r="184" spans="1:9" ht="30">
+      <c r="A184" s="10">
+        <v>46067</v>
+      </c>
+      <c r="B184" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C184" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D184" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E184" t="s">
+        <v>342</v>
+      </c>
+      <c r="H184" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="45">
+      <c r="A185" s="10">
+        <v>46064</v>
+      </c>
+      <c r="B185" s="10">
+        <v>46064</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E185" t="s">
+        <v>88</v>
+      </c>
+      <c r="H185" t="s">
+        <v>344</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" s="10">
+        <v>46065</v>
+      </c>
+      <c r="C186" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="E186" t="s">
+        <v>348</v>
+      </c>
+      <c r="H186" t="s">
+        <v>349</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" s="10">
+        <v>46066</v>
+      </c>
+      <c r="B187" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C187" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E187" t="s">
+        <v>75</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C188" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="E188" t="s">
+        <v>352</v>
+      </c>
+      <c r="G188">
+        <v>7</v>
+      </c>
+      <c r="H188" t="s">
+        <v>353</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="30">
+      <c r="A189" s="10">
+        <v>46067</v>
+      </c>
+      <c r="B189" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C189" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E189" t="s">
+        <v>356</v>
+      </c>
+      <c r="H189" t="s">
+        <v>358</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G159">
+  <autoFilter ref="A1:I159">
     <filterColumn colId="0">
       <filters>
         <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
@@ -6965,178 +7513,185 @@
         <dateGroupItem year="2025" month="12" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="1"/>
+    <filterColumn colId="7"/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1"/>
-    <hyperlink ref="G12" r:id="rId2"/>
-    <hyperlink ref="G17" r:id="rId3"/>
-    <hyperlink ref="G18" r:id="rId4"/>
-    <hyperlink ref="G2" r:id="rId5"/>
-    <hyperlink ref="G15" r:id="rId6"/>
-    <hyperlink ref="G5" r:id="rId7"/>
-    <hyperlink ref="G6" r:id="rId8"/>
-    <hyperlink ref="G7" r:id="rId9"/>
-    <hyperlink ref="G9" r:id="rId10"/>
-    <hyperlink ref="G11" r:id="rId11"/>
-    <hyperlink ref="G8" r:id="rId12"/>
-    <hyperlink ref="G22" r:id="rId13"/>
-    <hyperlink ref="G26" r:id="rId14"/>
-    <hyperlink ref="G27" r:id="rId15"/>
-    <hyperlink ref="G28" r:id="rId16"/>
-    <hyperlink ref="G30" r:id="rId17"/>
-    <hyperlink ref="G29" r:id="rId18"/>
-    <hyperlink ref="G33" r:id="rId19"/>
-    <hyperlink ref="G31" r:id="rId20"/>
-    <hyperlink ref="G32" r:id="rId21"/>
-    <hyperlink ref="G36" r:id="rId22"/>
-    <hyperlink ref="G34" r:id="rId23"/>
-    <hyperlink ref="G35" r:id="rId24"/>
-    <hyperlink ref="G39" r:id="rId25"/>
-    <hyperlink ref="G37" r:id="rId26"/>
-    <hyperlink ref="G38" r:id="rId27"/>
-    <hyperlink ref="G40" r:id="rId28"/>
-    <hyperlink ref="G41" r:id="rId29"/>
-    <hyperlink ref="G42" r:id="rId30"/>
-    <hyperlink ref="G45" r:id="rId31"/>
-    <hyperlink ref="G43" r:id="rId32"/>
-    <hyperlink ref="G44" r:id="rId33"/>
-    <hyperlink ref="G46" r:id="rId34"/>
-    <hyperlink ref="G47" r:id="rId35"/>
-    <hyperlink ref="G48" r:id="rId36"/>
-    <hyperlink ref="G49" r:id="rId37"/>
-    <hyperlink ref="G50" r:id="rId38"/>
-    <hyperlink ref="G51" r:id="rId39"/>
-    <hyperlink ref="G52" r:id="rId40"/>
-    <hyperlink ref="G53" r:id="rId41"/>
-    <hyperlink ref="G55" r:id="rId42"/>
-    <hyperlink ref="G54" r:id="rId43"/>
-    <hyperlink ref="G56" r:id="rId44"/>
-    <hyperlink ref="G60" r:id="rId45"/>
-    <hyperlink ref="G57" r:id="rId46"/>
-    <hyperlink ref="G58" r:id="rId47"/>
-    <hyperlink ref="G59" r:id="rId48"/>
-    <hyperlink ref="G61" r:id="rId49"/>
-    <hyperlink ref="G62" r:id="rId50"/>
-    <hyperlink ref="G63" r:id="rId51"/>
-    <hyperlink ref="G64" r:id="rId52"/>
-    <hyperlink ref="G65" r:id="rId53"/>
-    <hyperlink ref="G66" r:id="rId54"/>
-    <hyperlink ref="G67" r:id="rId55"/>
-    <hyperlink ref="G68" r:id="rId56"/>
-    <hyperlink ref="G70" r:id="rId57"/>
-    <hyperlink ref="G71" r:id="rId58"/>
-    <hyperlink ref="G72" r:id="rId59"/>
-    <hyperlink ref="G73" r:id="rId60"/>
-    <hyperlink ref="G74" r:id="rId61"/>
-    <hyperlink ref="G75" r:id="rId62"/>
-    <hyperlink ref="G76" r:id="rId63"/>
-    <hyperlink ref="G69" r:id="rId64"/>
-    <hyperlink ref="G77" r:id="rId65"/>
-    <hyperlink ref="G78" r:id="rId66"/>
-    <hyperlink ref="G79" r:id="rId67"/>
-    <hyperlink ref="G80" r:id="rId68"/>
-    <hyperlink ref="G81" r:id="rId69"/>
-    <hyperlink ref="G82" r:id="rId70"/>
-    <hyperlink ref="G83" r:id="rId71"/>
-    <hyperlink ref="G84" r:id="rId72"/>
-    <hyperlink ref="G85" r:id="rId73"/>
-    <hyperlink ref="G86" r:id="rId74"/>
-    <hyperlink ref="G87" r:id="rId75"/>
-    <hyperlink ref="G88" r:id="rId76"/>
-    <hyperlink ref="G89" r:id="rId77"/>
-    <hyperlink ref="G90" r:id="rId78"/>
-    <hyperlink ref="G91" r:id="rId79"/>
-    <hyperlink ref="G92" r:id="rId80"/>
-    <hyperlink ref="G93" r:id="rId81"/>
-    <hyperlink ref="G94" r:id="rId82"/>
-    <hyperlink ref="G95" r:id="rId83"/>
-    <hyperlink ref="G96" r:id="rId84"/>
-    <hyperlink ref="G97" r:id="rId85"/>
-    <hyperlink ref="G98" r:id="rId86"/>
-    <hyperlink ref="G99" r:id="rId87"/>
-    <hyperlink ref="G100" r:id="rId88"/>
-    <hyperlink ref="G101" r:id="rId89"/>
-    <hyperlink ref="G102" r:id="rId90"/>
-    <hyperlink ref="G103" r:id="rId91"/>
-    <hyperlink ref="G104" r:id="rId92"/>
-    <hyperlink ref="G105" r:id="rId93"/>
-    <hyperlink ref="G106" r:id="rId94"/>
-    <hyperlink ref="G108" r:id="rId95"/>
-    <hyperlink ref="G107" r:id="rId96"/>
-    <hyperlink ref="G109" r:id="rId97"/>
-    <hyperlink ref="G110" r:id="rId98"/>
-    <hyperlink ref="G111" r:id="rId99"/>
-    <hyperlink ref="G112" r:id="rId100"/>
-    <hyperlink ref="G113" r:id="rId101"/>
-    <hyperlink ref="G114" r:id="rId102"/>
-    <hyperlink ref="G115" r:id="rId103"/>
-    <hyperlink ref="G116" r:id="rId104"/>
-    <hyperlink ref="G117" r:id="rId105"/>
-    <hyperlink ref="G118" r:id="rId106"/>
-    <hyperlink ref="G119" r:id="rId107"/>
-    <hyperlink ref="G120" r:id="rId108"/>
-    <hyperlink ref="G121" r:id="rId109"/>
-    <hyperlink ref="G122" r:id="rId110"/>
-    <hyperlink ref="G123" r:id="rId111"/>
-    <hyperlink ref="G124" r:id="rId112"/>
-    <hyperlink ref="G125" r:id="rId113"/>
-    <hyperlink ref="G126" r:id="rId114"/>
-    <hyperlink ref="G127" r:id="rId115"/>
-    <hyperlink ref="G128" r:id="rId116"/>
-    <hyperlink ref="G129" r:id="rId117"/>
-    <hyperlink ref="G130" r:id="rId118"/>
-    <hyperlink ref="G131" r:id="rId119"/>
-    <hyperlink ref="G132" r:id="rId120"/>
-    <hyperlink ref="G133" r:id="rId121"/>
-    <hyperlink ref="G134" r:id="rId122"/>
-    <hyperlink ref="G135" r:id="rId123"/>
-    <hyperlink ref="G136" r:id="rId124"/>
-    <hyperlink ref="G137" r:id="rId125"/>
-    <hyperlink ref="G138" r:id="rId126"/>
-    <hyperlink ref="G139" r:id="rId127"/>
-    <hyperlink ref="G140" r:id="rId128"/>
-    <hyperlink ref="G142" r:id="rId129"/>
-    <hyperlink ref="G141" r:id="rId130"/>
-    <hyperlink ref="G143" r:id="rId131"/>
-    <hyperlink ref="G145" r:id="rId132"/>
-    <hyperlink ref="G146" r:id="rId133"/>
-    <hyperlink ref="G147" r:id="rId134"/>
-    <hyperlink ref="G148" r:id="rId135"/>
-    <hyperlink ref="G149" r:id="rId136"/>
-    <hyperlink ref="G158" r:id="rId137"/>
-    <hyperlink ref="G150" r:id="rId138"/>
-    <hyperlink ref="G151" r:id="rId139"/>
-    <hyperlink ref="G152" r:id="rId140"/>
-    <hyperlink ref="G153" r:id="rId141"/>
-    <hyperlink ref="G154" r:id="rId142"/>
-    <hyperlink ref="G155" r:id="rId143"/>
-    <hyperlink ref="G156" r:id="rId144"/>
-    <hyperlink ref="G157" r:id="rId145"/>
-    <hyperlink ref="G162" r:id="rId146"/>
-    <hyperlink ref="G163" r:id="rId147"/>
-    <hyperlink ref="G164" r:id="rId148"/>
-    <hyperlink ref="G165" r:id="rId149"/>
-    <hyperlink ref="G166" r:id="rId150"/>
-    <hyperlink ref="G167" r:id="rId151"/>
-    <hyperlink ref="G168" r:id="rId152"/>
-    <hyperlink ref="G169" r:id="rId153"/>
-    <hyperlink ref="G170" r:id="rId154"/>
-    <hyperlink ref="G171" r:id="rId155"/>
-    <hyperlink ref="G172" r:id="rId156"/>
-    <hyperlink ref="G173" r:id="rId157"/>
-    <hyperlink ref="G174" r:id="rId158"/>
-    <hyperlink ref="G175" r:id="rId159"/>
-    <hyperlink ref="G176" r:id="rId160"/>
-    <hyperlink ref="G177" r:id="rId161"/>
-    <hyperlink ref="G178" r:id="rId162"/>
-    <hyperlink ref="G179" r:id="rId163"/>
-    <hyperlink ref="G180" r:id="rId164"/>
-    <hyperlink ref="G181" r:id="rId165"/>
-    <hyperlink ref="G182" r:id="rId166"/>
-    <hyperlink ref="G183" r:id="rId167"/>
+    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I12" r:id="rId2"/>
+    <hyperlink ref="I17" r:id="rId3"/>
+    <hyperlink ref="I18" r:id="rId4"/>
+    <hyperlink ref="I2" r:id="rId5"/>
+    <hyperlink ref="I15" r:id="rId6"/>
+    <hyperlink ref="I5" r:id="rId7"/>
+    <hyperlink ref="I6" r:id="rId8"/>
+    <hyperlink ref="I7" r:id="rId9"/>
+    <hyperlink ref="I9" r:id="rId10"/>
+    <hyperlink ref="I11" r:id="rId11"/>
+    <hyperlink ref="I8" r:id="rId12"/>
+    <hyperlink ref="I22" r:id="rId13"/>
+    <hyperlink ref="I26" r:id="rId14"/>
+    <hyperlink ref="I27" r:id="rId15"/>
+    <hyperlink ref="I28" r:id="rId16"/>
+    <hyperlink ref="I30" r:id="rId17"/>
+    <hyperlink ref="I29" r:id="rId18"/>
+    <hyperlink ref="I33" r:id="rId19"/>
+    <hyperlink ref="I31" r:id="rId20"/>
+    <hyperlink ref="I32" r:id="rId21"/>
+    <hyperlink ref="I36" r:id="rId22"/>
+    <hyperlink ref="I34" r:id="rId23"/>
+    <hyperlink ref="I35" r:id="rId24"/>
+    <hyperlink ref="I39" r:id="rId25"/>
+    <hyperlink ref="I37" r:id="rId26"/>
+    <hyperlink ref="I38" r:id="rId27"/>
+    <hyperlink ref="I40" r:id="rId28"/>
+    <hyperlink ref="I41" r:id="rId29"/>
+    <hyperlink ref="I42" r:id="rId30"/>
+    <hyperlink ref="I45" r:id="rId31"/>
+    <hyperlink ref="I43" r:id="rId32"/>
+    <hyperlink ref="I44" r:id="rId33"/>
+    <hyperlink ref="I46" r:id="rId34"/>
+    <hyperlink ref="I47" r:id="rId35"/>
+    <hyperlink ref="I48" r:id="rId36"/>
+    <hyperlink ref="I49" r:id="rId37"/>
+    <hyperlink ref="I50" r:id="rId38"/>
+    <hyperlink ref="I51" r:id="rId39"/>
+    <hyperlink ref="I52" r:id="rId40"/>
+    <hyperlink ref="I53" r:id="rId41"/>
+    <hyperlink ref="I55" r:id="rId42"/>
+    <hyperlink ref="I54" r:id="rId43"/>
+    <hyperlink ref="I56" r:id="rId44"/>
+    <hyperlink ref="I60" r:id="rId45"/>
+    <hyperlink ref="I57" r:id="rId46"/>
+    <hyperlink ref="I58" r:id="rId47"/>
+    <hyperlink ref="I59" r:id="rId48"/>
+    <hyperlink ref="I61" r:id="rId49"/>
+    <hyperlink ref="I62" r:id="rId50"/>
+    <hyperlink ref="I63" r:id="rId51"/>
+    <hyperlink ref="I64" r:id="rId52"/>
+    <hyperlink ref="I65" r:id="rId53"/>
+    <hyperlink ref="I66" r:id="rId54"/>
+    <hyperlink ref="I67" r:id="rId55"/>
+    <hyperlink ref="I68" r:id="rId56"/>
+    <hyperlink ref="I70" r:id="rId57"/>
+    <hyperlink ref="I71" r:id="rId58"/>
+    <hyperlink ref="I72" r:id="rId59"/>
+    <hyperlink ref="I73" r:id="rId60"/>
+    <hyperlink ref="I74" r:id="rId61"/>
+    <hyperlink ref="I75" r:id="rId62"/>
+    <hyperlink ref="I76" r:id="rId63"/>
+    <hyperlink ref="I69" r:id="rId64"/>
+    <hyperlink ref="I77" r:id="rId65"/>
+    <hyperlink ref="I78" r:id="rId66"/>
+    <hyperlink ref="I79" r:id="rId67"/>
+    <hyperlink ref="I80" r:id="rId68"/>
+    <hyperlink ref="I81" r:id="rId69"/>
+    <hyperlink ref="I82" r:id="rId70"/>
+    <hyperlink ref="I83" r:id="rId71"/>
+    <hyperlink ref="I84" r:id="rId72"/>
+    <hyperlink ref="I85" r:id="rId73"/>
+    <hyperlink ref="I86" r:id="rId74"/>
+    <hyperlink ref="I87" r:id="rId75"/>
+    <hyperlink ref="I88" r:id="rId76"/>
+    <hyperlink ref="I89" r:id="rId77"/>
+    <hyperlink ref="I90" r:id="rId78"/>
+    <hyperlink ref="I91" r:id="rId79"/>
+    <hyperlink ref="I92" r:id="rId80"/>
+    <hyperlink ref="I93" r:id="rId81"/>
+    <hyperlink ref="I94" r:id="rId82"/>
+    <hyperlink ref="I95" r:id="rId83"/>
+    <hyperlink ref="I96" r:id="rId84"/>
+    <hyperlink ref="I97" r:id="rId85"/>
+    <hyperlink ref="I98" r:id="rId86"/>
+    <hyperlink ref="I99" r:id="rId87"/>
+    <hyperlink ref="I100" r:id="rId88"/>
+    <hyperlink ref="I101" r:id="rId89"/>
+    <hyperlink ref="I102" r:id="rId90"/>
+    <hyperlink ref="I103" r:id="rId91"/>
+    <hyperlink ref="I104" r:id="rId92"/>
+    <hyperlink ref="I105" r:id="rId93"/>
+    <hyperlink ref="I106" r:id="rId94"/>
+    <hyperlink ref="I108" r:id="rId95"/>
+    <hyperlink ref="I107" r:id="rId96"/>
+    <hyperlink ref="I109" r:id="rId97"/>
+    <hyperlink ref="I110" r:id="rId98"/>
+    <hyperlink ref="I111" r:id="rId99"/>
+    <hyperlink ref="I112" r:id="rId100"/>
+    <hyperlink ref="I113" r:id="rId101"/>
+    <hyperlink ref="I114" r:id="rId102"/>
+    <hyperlink ref="I115" r:id="rId103"/>
+    <hyperlink ref="I116" r:id="rId104"/>
+    <hyperlink ref="I117" r:id="rId105"/>
+    <hyperlink ref="I118" r:id="rId106"/>
+    <hyperlink ref="I119" r:id="rId107"/>
+    <hyperlink ref="I120" r:id="rId108"/>
+    <hyperlink ref="I121" r:id="rId109"/>
+    <hyperlink ref="I122" r:id="rId110"/>
+    <hyperlink ref="I123" r:id="rId111"/>
+    <hyperlink ref="I124" r:id="rId112"/>
+    <hyperlink ref="I125" r:id="rId113"/>
+    <hyperlink ref="I126" r:id="rId114"/>
+    <hyperlink ref="I127" r:id="rId115"/>
+    <hyperlink ref="I128" r:id="rId116"/>
+    <hyperlink ref="I129" r:id="rId117"/>
+    <hyperlink ref="I130" r:id="rId118"/>
+    <hyperlink ref="I131" r:id="rId119"/>
+    <hyperlink ref="I132" r:id="rId120"/>
+    <hyperlink ref="I133" r:id="rId121"/>
+    <hyperlink ref="I134" r:id="rId122"/>
+    <hyperlink ref="I135" r:id="rId123"/>
+    <hyperlink ref="I136" r:id="rId124"/>
+    <hyperlink ref="I137" r:id="rId125"/>
+    <hyperlink ref="I138" r:id="rId126"/>
+    <hyperlink ref="I139" r:id="rId127"/>
+    <hyperlink ref="I140" r:id="rId128"/>
+    <hyperlink ref="I142" r:id="rId129"/>
+    <hyperlink ref="I141" r:id="rId130"/>
+    <hyperlink ref="I143" r:id="rId131"/>
+    <hyperlink ref="I145" r:id="rId132"/>
+    <hyperlink ref="I146" r:id="rId133"/>
+    <hyperlink ref="I147" r:id="rId134"/>
+    <hyperlink ref="I148" r:id="rId135"/>
+    <hyperlink ref="I149" r:id="rId136"/>
+    <hyperlink ref="I158" r:id="rId137"/>
+    <hyperlink ref="I150" r:id="rId138"/>
+    <hyperlink ref="I151" r:id="rId139"/>
+    <hyperlink ref="I152" r:id="rId140"/>
+    <hyperlink ref="I153" r:id="rId141"/>
+    <hyperlink ref="I154" r:id="rId142"/>
+    <hyperlink ref="I155" r:id="rId143"/>
+    <hyperlink ref="I156" r:id="rId144"/>
+    <hyperlink ref="I157" r:id="rId145"/>
+    <hyperlink ref="I162" r:id="rId146"/>
+    <hyperlink ref="I163" r:id="rId147"/>
+    <hyperlink ref="I164" r:id="rId148"/>
+    <hyperlink ref="I165" r:id="rId149"/>
+    <hyperlink ref="I166" r:id="rId150"/>
+    <hyperlink ref="I167" r:id="rId151"/>
+    <hyperlink ref="I168" r:id="rId152"/>
+    <hyperlink ref="I169" r:id="rId153"/>
+    <hyperlink ref="I170" r:id="rId154"/>
+    <hyperlink ref="I171" r:id="rId155"/>
+    <hyperlink ref="I172" r:id="rId156"/>
+    <hyperlink ref="I173" r:id="rId157"/>
+    <hyperlink ref="I174" r:id="rId158"/>
+    <hyperlink ref="I175" r:id="rId159"/>
+    <hyperlink ref="I176" r:id="rId160"/>
+    <hyperlink ref="I177" r:id="rId161"/>
+    <hyperlink ref="I178" r:id="rId162"/>
+    <hyperlink ref="I179" r:id="rId163"/>
+    <hyperlink ref="I180" r:id="rId164"/>
+    <hyperlink ref="I181" r:id="rId165"/>
+    <hyperlink ref="I182" r:id="rId166"/>
+    <hyperlink ref="I183" r:id="rId167"/>
+    <hyperlink ref="I185" r:id="rId168"/>
+    <hyperlink ref="I186" r:id="rId169"/>
+    <hyperlink ref="I187" r:id="rId170"/>
+    <hyperlink ref="I188" r:id="rId171"/>
+    <hyperlink ref="I189" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId168"/>
+  <pageSetup orientation="portrait" r:id="rId173"/>
 </worksheet>
 </file>
 

--- a/Marine_Operations_Performance_Dataset.xlsx
+++ b/Marine_Operations_Performance_Dataset.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$197</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="366">
   <si>
     <t>DATE</t>
   </si>
@@ -1102,6 +1102,27 @@
   </si>
   <si>
     <t>Administration</t>
+  </si>
+  <si>
+    <t>AIP Nyakahemura</t>
+  </si>
+  <si>
+    <t>AIP Jakech and AIP Egesa</t>
+  </si>
+  <si>
+    <t>BaBa TV</t>
+  </si>
+  <si>
+    <t>KK beach</t>
+  </si>
+  <si>
+    <t>Ministry of Works and Transport</t>
+  </si>
+  <si>
+    <t>Handover of Drowning Prevention strategy to Marine unit</t>
+  </si>
+  <si>
+    <t>Handover of Drowning Prevention Strategy to the Marine unit</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1130,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1259,7 +1280,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3346,8 +3367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3388,7 +3408,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="46.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="46.5" customHeight="1" thickBot="1">
       <c r="A2" s="3">
         <v>45751</v>
       </c>
@@ -3413,7 +3433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="A3" s="3">
         <v>45756</v>
       </c>
@@ -3438,7 +3458,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="4" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="A4" s="3">
         <v>45758</v>
       </c>
@@ -3459,7 +3479,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="5" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="A5" s="3">
         <v>45771</v>
       </c>
@@ -3484,7 +3504,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="37.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="6" spans="1:9" ht="37.5" customHeight="1" thickBot="1">
       <c r="A6" s="3">
         <v>45772</v>
       </c>
@@ -3509,7 +3529,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="7" spans="1:9" ht="36.75" customHeight="1" thickBot="1">
       <c r="A7" s="3">
         <v>45756</v>
       </c>
@@ -3534,7 +3554,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="8" spans="1:9" ht="36.75" customHeight="1" thickBot="1">
       <c r="A8" s="3">
         <v>45797</v>
       </c>
@@ -3557,7 +3577,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="9" spans="1:9" ht="36.75" customHeight="1" thickBot="1">
       <c r="A9" s="3">
         <v>45813</v>
       </c>
@@ -3578,7 +3598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="10" spans="1:9" ht="36.75" customHeight="1" thickBot="1">
       <c r="A10" s="3">
         <v>45818</v>
       </c>
@@ -3603,7 +3623,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="36.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="11" spans="1:9" ht="36.75" customHeight="1" thickBot="1">
       <c r="A11" s="3">
         <v>45821</v>
       </c>
@@ -3628,7 +3648,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="34.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="12" spans="1:9" ht="34.5" customHeight="1" thickBot="1">
       <c r="A12" s="3">
         <v>45828</v>
       </c>
@@ -3649,7 +3669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="13" spans="1:9" ht="45.75" thickBot="1">
       <c r="A13" s="3">
         <v>45828</v>
       </c>
@@ -3668,7 +3688,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="14" spans="1:9" ht="45.75" thickBot="1">
       <c r="A14" s="3">
         <v>45828</v>
       </c>
@@ -3687,7 +3707,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="15" spans="1:9" ht="30.75" thickBot="1">
       <c r="A15" s="3">
         <v>45809</v>
       </c>
@@ -3710,7 +3730,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="16" spans="1:9" ht="30.75" thickBot="1">
       <c r="A16" s="3">
         <v>45839</v>
       </c>
@@ -3729,7 +3749,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="17" spans="1:9" ht="45.75" thickBot="1">
       <c r="A17" s="3">
         <v>45840</v>
       </c>
@@ -3752,7 +3772,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="18" spans="1:9" ht="30.75" thickBot="1">
       <c r="A18" s="3">
         <v>45840</v>
       </c>
@@ -3775,7 +3795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="19" spans="1:9" ht="30.75" thickBot="1">
       <c r="A19" s="3">
         <v>45841</v>
       </c>
@@ -3794,7 +3814,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" ht="15.75" hidden="1" thickBot="1">
+    <row r="20" spans="1:9" ht="15.75" thickBot="1">
       <c r="A20" s="3">
         <v>45842</v>
       </c>
@@ -3809,7 +3829,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="21" spans="1:9" ht="45.75" thickBot="1">
       <c r="A21" s="3">
         <v>45843</v>
       </c>
@@ -3830,7 +3850,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="22" spans="1:9" ht="30.75" thickBot="1">
       <c r="A22" s="3">
         <v>45847</v>
       </c>
@@ -3853,7 +3873,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="23" spans="1:9" ht="30.75" thickBot="1">
       <c r="A23" s="3">
         <v>45863</v>
       </c>
@@ -3876,7 +3896,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="24" spans="1:9" ht="30.75" thickBot="1">
       <c r="A24" s="3">
         <v>45847</v>
       </c>
@@ -3897,7 +3917,7 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="25" spans="1:9" ht="45.75" thickBot="1">
       <c r="A25" s="3">
         <v>45877</v>
       </c>
@@ -3920,7 +3940,7 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="26" spans="1:9" ht="30.75" thickBot="1">
       <c r="A26" s="3">
         <v>45891</v>
       </c>
@@ -3943,7 +3963,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="27" spans="1:9" ht="30.75" thickBot="1">
       <c r="A27" s="3">
         <v>45870</v>
       </c>
@@ -3966,7 +3986,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="28" spans="1:9" ht="30.75" thickBot="1">
       <c r="A28" s="3">
         <v>45894</v>
       </c>
@@ -3991,7 +4011,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="60.75" hidden="1" thickBot="1">
+    <row r="29" spans="1:9" ht="60.75" thickBot="1">
       <c r="A29" s="3">
         <v>45894</v>
       </c>
@@ -4016,7 +4036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" hidden="1" thickBot="1">
+    <row r="30" spans="1:9" ht="15.75" thickBot="1">
       <c r="A30" s="3">
         <v>45894</v>
       </c>
@@ -4037,7 +4057,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="31" spans="1:9" ht="30.75" thickBot="1">
       <c r="A31" s="3">
         <v>45896</v>
       </c>
@@ -4060,7 +4080,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="60.75" hidden="1" thickBot="1">
+    <row r="32" spans="1:9" ht="60.75" thickBot="1">
       <c r="A32" s="3">
         <v>45896</v>
       </c>
@@ -4085,7 +4105,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="33" spans="1:9" ht="45.75" thickBot="1">
       <c r="A33" s="3">
         <v>45896</v>
       </c>
@@ -4108,7 +4128,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="34" spans="1:9" ht="45.75" thickBot="1">
       <c r="A34" s="3">
         <v>45897</v>
       </c>
@@ -4133,7 +4153,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="35" spans="1:9" ht="45.75" thickBot="1">
       <c r="A35" s="3">
         <v>45897</v>
       </c>
@@ -4158,7 +4178,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="36" spans="1:9" ht="30.75" thickBot="1">
       <c r="A36" s="3">
         <v>45897</v>
       </c>
@@ -4181,7 +4201,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="37" spans="1:9" ht="45.75" thickBot="1">
       <c r="A37" s="3">
         <v>45899</v>
       </c>
@@ -4206,7 +4226,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="38" spans="1:9" ht="30.75" thickBot="1">
       <c r="A38" s="3">
         <v>45903</v>
       </c>
@@ -4227,7 +4247,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="60.75" hidden="1" thickBot="1">
+    <row r="39" spans="1:9" ht="60.75" thickBot="1">
       <c r="A39" s="3">
         <v>45898</v>
       </c>
@@ -4250,7 +4270,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="40" spans="1:9" ht="45.75" thickBot="1">
       <c r="A40" s="3">
         <v>45903</v>
       </c>
@@ -4273,7 +4293,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="41" spans="1:9" ht="45.75" thickBot="1">
       <c r="A41" s="3">
         <v>45904</v>
       </c>
@@ -4296,7 +4316,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="42" spans="1:9" ht="30.75" thickBot="1">
       <c r="A42" s="3">
         <v>45904</v>
       </c>
@@ -4319,7 +4339,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="43" spans="1:9" ht="30.75" thickBot="1">
       <c r="A43" s="3">
         <v>45905</v>
       </c>
@@ -4342,7 +4362,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="44" spans="1:9" ht="30.75" thickBot="1">
       <c r="A44" s="3">
         <v>45905</v>
       </c>
@@ -4365,7 +4385,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="45" spans="1:9" ht="30.75" thickBot="1">
       <c r="A45" s="3">
         <v>45905</v>
       </c>
@@ -4388,7 +4408,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="46" spans="1:9" ht="30.75" thickBot="1">
       <c r="A46" s="3">
         <v>45905</v>
       </c>
@@ -4409,7 +4429,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="47" spans="1:9" ht="45.75" thickBot="1">
       <c r="A47" s="3">
         <v>45906</v>
       </c>
@@ -4432,7 +4452,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="48" spans="1:9" ht="45.75" thickBot="1">
       <c r="A48" s="3">
         <v>45910</v>
       </c>
@@ -4457,7 +4477,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="75.75" hidden="1" thickBot="1">
+    <row r="49" spans="1:9" ht="75.75" thickBot="1">
       <c r="A49" s="3">
         <v>45908</v>
       </c>
@@ -4482,7 +4502,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="60.75" hidden="1" thickBot="1">
+    <row r="50" spans="1:9" ht="60.75" thickBot="1">
       <c r="A50" s="3">
         <v>45909</v>
       </c>
@@ -4505,7 +4525,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="75.75" hidden="1" thickBot="1">
+    <row r="51" spans="1:9" ht="75.75" thickBot="1">
       <c r="A51" s="3">
         <v>45911</v>
       </c>
@@ -4530,7 +4550,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="52" spans="1:9" ht="45.75" thickBot="1">
       <c r="A52" s="3">
         <v>45911</v>
       </c>
@@ -4555,7 +4575,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="53" spans="1:9" ht="30.75" thickBot="1">
       <c r="A53" s="3">
         <v>45913</v>
       </c>
@@ -4578,7 +4598,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="54" spans="1:9" ht="30.75" thickBot="1">
       <c r="A54" s="3">
         <v>45916</v>
       </c>
@@ -4599,7 +4619,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="55" spans="1:9" ht="30.75" thickBot="1">
       <c r="A55" s="3">
         <v>45915</v>
       </c>
@@ -4622,7 +4642,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="56" spans="1:9" ht="45.75" thickBot="1">
       <c r="A56" s="3">
         <v>45916</v>
       </c>
@@ -4645,7 +4665,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="57" spans="1:9" ht="30.75" thickBot="1">
       <c r="A57" s="3">
         <v>45917</v>
       </c>
@@ -4666,7 +4686,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="58" spans="1:9" ht="45.75" thickBot="1">
       <c r="A58" s="3">
         <v>45919</v>
       </c>
@@ -4689,7 +4709,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" hidden="1" thickBot="1">
+    <row r="59" spans="1:9" ht="15.75" thickBot="1">
       <c r="A59" s="3">
         <v>45919</v>
       </c>
@@ -4710,7 +4730,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="60" spans="1:9" ht="45.75" thickBot="1">
       <c r="A60" s="3">
         <v>45916</v>
       </c>
@@ -4733,7 +4753,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="61" spans="1:9" ht="30.75" thickBot="1">
       <c r="A61" s="3">
         <v>45922</v>
       </c>
@@ -4756,7 +4776,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="62" spans="1:9" ht="30.75" thickBot="1">
       <c r="A62" s="3">
         <v>45923</v>
       </c>
@@ -4779,7 +4799,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="63" spans="1:9" ht="45.75" thickBot="1">
       <c r="A63" s="3">
         <v>45924</v>
       </c>
@@ -4802,7 +4822,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="64" spans="1:9" ht="45.75" thickBot="1">
       <c r="A64" s="3">
         <v>45924</v>
       </c>
@@ -4827,7 +4847,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="60.75" hidden="1" thickBot="1">
+    <row r="65" spans="1:9" ht="60.75" thickBot="1">
       <c r="A65" s="3">
         <v>45925</v>
       </c>
@@ -4850,7 +4870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="90.75" hidden="1" thickBot="1">
+    <row r="66" spans="1:9" ht="90.75" thickBot="1">
       <c r="A66" s="3">
         <v>45926</v>
       </c>
@@ -4873,7 +4893,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="67" spans="1:9" ht="30.75" thickBot="1">
       <c r="A67" s="3">
         <v>45930</v>
       </c>
@@ -4896,7 +4916,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30.75" hidden="1" thickBot="1">
+    <row r="68" spans="1:9" ht="30.75" thickBot="1">
       <c r="A68" s="3">
         <v>45930</v>
       </c>
@@ -4919,7 +4939,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="45.75" hidden="1" thickBot="1">
+    <row r="69" spans="1:9" ht="45.75" thickBot="1">
       <c r="A69" s="3"/>
       <c r="B69" s="14"/>
       <c r="C69" s="1" t="s">
@@ -6913,7 +6933,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="61.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="159" spans="1:9" ht="61.5" customHeight="1" thickBot="1">
       <c r="A159" s="3">
         <v>45890</v>
       </c>
@@ -7504,15 +7524,249 @@
         <v>325</v>
       </c>
     </row>
+    <row r="190" spans="1:9" ht="30">
+      <c r="A190" s="10">
+        <v>46070</v>
+      </c>
+      <c r="B190" s="10">
+        <v>46070</v>
+      </c>
+      <c r="C190" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E190" t="s">
+        <v>90</v>
+      </c>
+      <c r="G190">
+        <v>15</v>
+      </c>
+      <c r="H190" t="s">
+        <v>358</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B191" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C191" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E191" t="s">
+        <v>100</v>
+      </c>
+      <c r="H191" t="s">
+        <v>344</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="30">
+      <c r="A192" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B192" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C192" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" t="s">
+        <v>322</v>
+      </c>
+      <c r="G192">
+        <v>100</v>
+      </c>
+      <c r="H192" t="s">
+        <v>358</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="30">
+      <c r="A193" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B193" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C193" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E193" t="s">
+        <v>100</v>
+      </c>
+      <c r="H193" t="s">
+        <v>344</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="30">
+      <c r="A194" s="10">
+        <v>46072</v>
+      </c>
+      <c r="B194" s="10">
+        <v>46072</v>
+      </c>
+      <c r="C194" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E194" t="s">
+        <v>356</v>
+      </c>
+      <c r="H194" t="s">
+        <v>358</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" s="10">
+        <v>46069</v>
+      </c>
+      <c r="B195" s="10">
+        <v>46069</v>
+      </c>
+      <c r="C195" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E195" t="s">
+        <v>44</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="30">
+      <c r="A196" s="10">
+        <v>46071</v>
+      </c>
+      <c r="B196" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C196" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E196" t="s">
+        <v>75</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="10">
+        <v>46072</v>
+      </c>
+      <c r="E197" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" s="10">
+        <v>46072</v>
+      </c>
+      <c r="E198" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" s="10">
+        <v>46074</v>
+      </c>
+      <c r="B199" s="10">
+        <v>46074</v>
+      </c>
+      <c r="C199" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D199" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E199" t="s">
+        <v>100</v>
+      </c>
+      <c r="H199" t="s">
+        <v>343</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" s="10">
+        <v>46076</v>
+      </c>
+      <c r="B200" s="10">
+        <v>46076</v>
+      </c>
+      <c r="C200" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E200" t="s">
+        <v>81</v>
+      </c>
+      <c r="H200" t="s">
+        <v>344</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="45">
+      <c r="A201" s="10">
+        <v>46078</v>
+      </c>
+      <c r="B201" s="10">
+        <v>46078</v>
+      </c>
+      <c r="C201" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E201" t="s">
+        <v>364</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I159">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2025" month="10" dateTimeGrouping="month"/>
-        <dateGroupItem year="2025" month="11" dateTimeGrouping="month"/>
-        <dateGroupItem year="2025" month="12" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:I197">
+    <filterColumn colId="0"/>
     <filterColumn colId="1"/>
     <filterColumn colId="7"/>
   </autoFilter>
@@ -7689,9 +7943,19 @@
     <hyperlink ref="I187" r:id="rId170"/>
     <hyperlink ref="I188" r:id="rId171"/>
     <hyperlink ref="I189" r:id="rId172"/>
+    <hyperlink ref="I190" r:id="rId173"/>
+    <hyperlink ref="I191" r:id="rId174"/>
+    <hyperlink ref="I192" r:id="rId175"/>
+    <hyperlink ref="I193" r:id="rId176"/>
+    <hyperlink ref="I194" r:id="rId177"/>
+    <hyperlink ref="I195" r:id="rId178"/>
+    <hyperlink ref="I196" r:id="rId179"/>
+    <hyperlink ref="I199" r:id="rId180"/>
+    <hyperlink ref="I200" r:id="rId181"/>
+    <hyperlink ref="I201" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId173"/>
+  <pageSetup orientation="portrait" r:id="rId183"/>
 </worksheet>
 </file>
 
